--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118660154</v>
+        <v>118660177</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588533</v>
+        <v>588481</v>
       </c>
       <c r="R3" t="n">
-        <v>6435671</v>
+        <v>6435677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118660177</v>
+        <v>118660154</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588481</v>
+        <v>588533</v>
       </c>
       <c r="R4" t="n">
-        <v>6435677</v>
+        <v>6435671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118660460</v>
+        <v>118660127</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588536</v>
+        <v>588502</v>
       </c>
       <c r="R5" t="n">
-        <v>6435708</v>
+        <v>6435703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118660127</v>
+        <v>118660250</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1162,7 +1162,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1171,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588502</v>
+        <v>588475</v>
       </c>
       <c r="R6" t="n">
-        <v>6435703</v>
+        <v>6435672</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118660250</v>
+        <v>118660460</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1273,11 +1277,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588475</v>
+        <v>588536</v>
       </c>
       <c r="R7" t="n">
-        <v>6435672</v>
+        <v>6435708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118810141</v>
+        <v>118810096</v>
       </c>
       <c r="B9" t="n">
-        <v>96804</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,38 +1475,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588532</v>
+        <v>588597</v>
       </c>
       <c r="R9" t="n">
-        <v>6435805</v>
+        <v>6435628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809127</v>
+        <v>118809147</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1617,7 +1617,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1626,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588555</v>
+        <v>588559</v>
       </c>
       <c r="R10" t="n">
-        <v>6435705</v>
+        <v>6435691</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118660416</v>
+        <v>118809025</v>
       </c>
       <c r="B11" t="n">
-        <v>89999</v>
+        <v>94620</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,38 +1705,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1740,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588568</v>
+        <v>588501</v>
       </c>
       <c r="R11" t="n">
-        <v>6435711</v>
+        <v>6435835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,12 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809025</v>
+        <v>118809053</v>
       </c>
       <c r="B12" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,29 +1812,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1847,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588501</v>
+        <v>588559</v>
       </c>
       <c r="R12" t="n">
-        <v>6435835</v>
+        <v>6435712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809147</v>
+        <v>118810141</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>96804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,38 +1923,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588559</v>
+        <v>588532</v>
       </c>
       <c r="R13" t="n">
-        <v>6435691</v>
+        <v>6435805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809053</v>
+        <v>118660416</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,31 +2042,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588559</v>
+        <v>588568</v>
       </c>
       <c r="R14" t="n">
-        <v>6435712</v>
+        <v>6435711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,12 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2140,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118810096</v>
+        <v>118809127</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2175,11 +2179,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588597</v>
+        <v>588555</v>
       </c>
       <c r="R15" t="n">
-        <v>6435628</v>
+        <v>6435705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118660232</v>
+        <v>118660127</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -708,11 +708,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588470</v>
+        <v>588502</v>
       </c>
       <c r="R2" t="n">
-        <v>6435670</v>
+        <v>6435703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118660177</v>
+        <v>118660232</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -823,7 +819,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588481</v>
+        <v>588470</v>
       </c>
       <c r="R3" t="n">
-        <v>6435677</v>
+        <v>6435670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118660154</v>
+        <v>118660250</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -940,7 +940,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -949,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588533</v>
+        <v>588475</v>
       </c>
       <c r="R4" t="n">
-        <v>6435671</v>
+        <v>6435672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118660127</v>
+        <v>118660460</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1060,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588502</v>
+        <v>588536</v>
       </c>
       <c r="R5" t="n">
-        <v>6435703</v>
+        <v>6435708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118660250</v>
+        <v>118660154</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1162,11 +1166,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588475</v>
+        <v>588533</v>
       </c>
       <c r="R6" t="n">
-        <v>6435672</v>
+        <v>6435671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118660460</v>
+        <v>118660177</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588536</v>
+        <v>588481</v>
       </c>
       <c r="R7" t="n">
-        <v>6435708</v>
+        <v>6435677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118810096</v>
+        <v>118809025</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,38 +1475,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588597</v>
+        <v>588501</v>
       </c>
       <c r="R9" t="n">
-        <v>6435628</v>
+        <v>6435835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809147</v>
+        <v>118660416</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>89999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,35 +1586,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1630,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588559</v>
+        <v>588568</v>
       </c>
       <c r="R10" t="n">
-        <v>6435691</v>
+        <v>6435711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,12 +1651,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809025</v>
+        <v>118810096</v>
       </c>
       <c r="B11" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,30 +1696,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1737,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588501</v>
+        <v>588597</v>
       </c>
       <c r="R11" t="n">
-        <v>6435835</v>
+        <v>6435628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2026,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118660416</v>
+        <v>118809127</v>
       </c>
       <c r="B14" t="n">
-        <v>89999</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,34 +2041,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2077,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588568</v>
+        <v>588555</v>
       </c>
       <c r="R14" t="n">
-        <v>6435711</v>
+        <v>6435705</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,12 +2103,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809127</v>
+        <v>118809147</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2179,7 +2175,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588555</v>
+        <v>588559</v>
       </c>
       <c r="R15" t="n">
-        <v>6435705</v>
+        <v>6435691</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118660127</v>
+        <v>118660250</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -714,7 +714,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588502</v>
+        <v>588475</v>
       </c>
       <c r="R2" t="n">
-        <v>6435703</v>
+        <v>6435672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118660232</v>
+        <v>118660460</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,11 +823,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588470</v>
+        <v>588536</v>
       </c>
       <c r="R3" t="n">
-        <v>6435670</v>
+        <v>6435708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118660250</v>
+        <v>118660232</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588475</v>
+        <v>588470</v>
       </c>
       <c r="R4" t="n">
-        <v>6435672</v>
+        <v>6435670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118660460</v>
+        <v>118660154</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588536</v>
+        <v>588533</v>
       </c>
       <c r="R5" t="n">
-        <v>6435708</v>
+        <v>6435671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118660154</v>
+        <v>118660127</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588533</v>
+        <v>588502</v>
       </c>
       <c r="R6" t="n">
-        <v>6435671</v>
+        <v>6435703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1241,7 @@
         <v>118660177</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118809025</v>
+        <v>118810096</v>
       </c>
       <c r="B9" t="n">
-        <v>94620</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,30 +1475,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1507,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588501</v>
+        <v>588597</v>
       </c>
       <c r="R9" t="n">
-        <v>6435835</v>
+        <v>6435628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118660416</v>
+        <v>118809053</v>
       </c>
       <c r="B10" t="n">
-        <v>89999</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,34 +1594,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588568</v>
+        <v>588559</v>
       </c>
       <c r="R10" t="n">
-        <v>6435711</v>
+        <v>6435712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,12 +1656,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118810096</v>
+        <v>118809147</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588597</v>
+        <v>588559</v>
       </c>
       <c r="R11" t="n">
-        <v>6435628</v>
+        <v>6435691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809053</v>
+        <v>118809025</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,33 +1816,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1847,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588559</v>
+        <v>588501</v>
       </c>
       <c r="R12" t="n">
-        <v>6435712</v>
+        <v>6435835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118810141</v>
+        <v>118809127</v>
       </c>
       <c r="B13" t="n">
-        <v>96804</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,35 +1923,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1962,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588532</v>
+        <v>588555</v>
       </c>
       <c r="R13" t="n">
-        <v>6435805</v>
+        <v>6435705</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809127</v>
+        <v>118660416</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>90006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,31 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588555</v>
+        <v>588568</v>
       </c>
       <c r="R14" t="n">
-        <v>6435705</v>
+        <v>6435711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809147</v>
+        <v>118810141</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>96811</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,38 +2148,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588559</v>
+        <v>588532</v>
       </c>
       <c r="R15" t="n">
-        <v>6435691</v>
+        <v>6435805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118660460</v>
+        <v>118660232</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -823,7 +823,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588536</v>
+        <v>588470</v>
       </c>
       <c r="R3" t="n">
-        <v>6435708</v>
+        <v>6435670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118660232</v>
+        <v>118660460</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -934,11 +938,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588470</v>
+        <v>588536</v>
       </c>
       <c r="R4" t="n">
-        <v>6435670</v>
+        <v>6435708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118660250</v>
+        <v>118660232</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -708,17 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588475</v>
+        <v>588470</v>
       </c>
       <c r="R2" t="n">
-        <v>6435672</v>
+        <v>6435670</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118660232</v>
+        <v>118660154</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -823,11 +823,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -842,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588470</v>
+        <v>588533</v>
       </c>
       <c r="R3" t="n">
-        <v>6435670</v>
+        <v>6435671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118660460</v>
+        <v>118660250</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -944,7 +940,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588536</v>
+        <v>588475</v>
       </c>
       <c r="R4" t="n">
-        <v>6435708</v>
+        <v>6435672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118660154</v>
+        <v>118660127</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588533</v>
+        <v>588502</v>
       </c>
       <c r="R5" t="n">
-        <v>6435671</v>
+        <v>6435703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118660127</v>
+        <v>118660460</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588502</v>
+        <v>588536</v>
       </c>
       <c r="R6" t="n">
-        <v>6435703</v>
+        <v>6435708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118810096</v>
+        <v>118809053</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1502,11 +1502,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588597</v>
+        <v>588559</v>
       </c>
       <c r="R9" t="n">
-        <v>6435628</v>
+        <v>6435712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809053</v>
+        <v>118809025</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,33 +1586,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1626,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588559</v>
+        <v>588501</v>
       </c>
       <c r="R10" t="n">
-        <v>6435712</v>
+        <v>6435835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809147</v>
+        <v>118660416</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>90006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,35 +1697,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1741,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588559</v>
+        <v>588568</v>
       </c>
       <c r="R11" t="n">
-        <v>6435691</v>
+        <v>6435711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,12 +1762,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809025</v>
+        <v>118810096</v>
       </c>
       <c r="B12" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,30 +1807,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588501</v>
+        <v>588597</v>
       </c>
       <c r="R12" t="n">
-        <v>6435835</v>
+        <v>6435628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809127</v>
+        <v>118810141</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
+        <v>96811</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,31 +1922,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1959,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588555</v>
+        <v>588532</v>
       </c>
       <c r="R13" t="n">
-        <v>6435705</v>
+        <v>6435805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118660416</v>
+        <v>118809147</v>
       </c>
       <c r="B14" t="n">
-        <v>90006</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,34 +2041,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588568</v>
+        <v>588559</v>
       </c>
       <c r="R14" t="n">
-        <v>6435711</v>
+        <v>6435691</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,12 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118810141</v>
+        <v>118809127</v>
       </c>
       <c r="B15" t="n">
-        <v>96811</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,35 +2152,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588532</v>
+        <v>588555</v>
       </c>
       <c r="R15" t="n">
-        <v>6435805</v>
+        <v>6435705</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2251,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750227</v>
+        <v>119750060</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,35 +2263,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588526</v>
+        <v>588510</v>
       </c>
       <c r="R16" t="n">
-        <v>6435798</v>
+        <v>6435794</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119750194</v>
+        <v>119749642</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>56522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,49 +2381,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588531</v>
+        <v>588609</v>
       </c>
       <c r="R17" t="n">
-        <v>6435803</v>
+        <v>6435665</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,13 +2455,17 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2584,17 +2588,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119749642</v>
+        <v>119750021</v>
       </c>
       <c r="B19" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2611,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2629,24 +2633,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588609</v>
+        <v>588537</v>
       </c>
       <c r="R19" t="n">
-        <v>6435665</v>
+        <v>6435763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2681,17 +2684,13 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2710,10 +2709,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750060</v>
+        <v>119750194</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>96865</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,34 +2725,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588510</v>
+        <v>588531</v>
       </c>
       <c r="R20" t="n">
-        <v>6435794</v>
+        <v>6435803</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119750021</v>
+        <v>119750227</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,35 +2836,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588537</v>
+        <v>588526</v>
       </c>
       <c r="R21" t="n">
-        <v>6435763</v>
+        <v>6435798</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2251,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750060</v>
+        <v>119750021</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588510</v>
+        <v>588537</v>
       </c>
       <c r="R16" t="n">
-        <v>6435794</v>
+        <v>6435763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749642</v>
+        <v>119750194</v>
       </c>
       <c r="B17" t="n">
-        <v>56522</v>
+        <v>96865</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,49 +2381,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588609</v>
+        <v>588531</v>
       </c>
       <c r="R17" t="n">
-        <v>6435665</v>
+        <v>6435803</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,17 +2455,13 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119750021</v>
+        <v>119749642</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2633,23 +2629,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588537</v>
+        <v>588609</v>
       </c>
       <c r="R19" t="n">
-        <v>6435763</v>
+        <v>6435665</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,13 +2681,17 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2709,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750194</v>
+        <v>119750227</v>
       </c>
       <c r="B20" t="n">
-        <v>96865</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,39 +2722,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588531</v>
+        <v>588526</v>
       </c>
       <c r="R20" t="n">
-        <v>6435803</v>
+        <v>6435798</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119750227</v>
+        <v>119750060</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,35 +2836,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588526</v>
+        <v>588510</v>
       </c>
       <c r="R21" t="n">
-        <v>6435798</v>
+        <v>6435794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2251,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750021</v>
+        <v>119750227</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,35 +2263,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588537</v>
+        <v>588526</v>
       </c>
       <c r="R16" t="n">
-        <v>6435763</v>
+        <v>6435798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119750194</v>
+        <v>119749574</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,35 +2377,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2413,17 +2409,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588531</v>
+        <v>588618</v>
       </c>
       <c r="R17" t="n">
-        <v>6435803</v>
+        <v>6435661</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749574</v>
+        <v>119750021</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,46 +2488,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588618</v>
+        <v>588537</v>
       </c>
       <c r="R18" t="n">
-        <v>6435661</v>
+        <v>6435763</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,10 +2709,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750227</v>
+        <v>119750060</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,35 +2721,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588526</v>
+        <v>588510</v>
       </c>
       <c r="R20" t="n">
-        <v>6435798</v>
+        <v>6435794</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119750060</v>
+        <v>119750194</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>96865</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2840,34 +2839,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588510</v>
+        <v>588531</v>
       </c>
       <c r="R21" t="n">
-        <v>6435794</v>
+        <v>6435803</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749574</v>
+        <v>119750021</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,46 +2377,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588618</v>
+        <v>588537</v>
       </c>
       <c r="R17" t="n">
-        <v>6435661</v>
+        <v>6435763</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119750021</v>
+        <v>119749574</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,49 +2491,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588537</v>
+        <v>588618</v>
       </c>
       <c r="R18" t="n">
-        <v>6435763</v>
+        <v>6435661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119750021</v>
+        <v>119749574</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,49 +2377,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588537</v>
+        <v>588618</v>
       </c>
       <c r="R17" t="n">
-        <v>6435763</v>
+        <v>6435661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119749574</v>
+        <v>119750021</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,46 +2488,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588618</v>
+        <v>588537</v>
       </c>
       <c r="R18" t="n">
-        <v>6435661</v>
+        <v>6435763</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 27378-2024 artfynd.xlsx
+++ b/artfynd/A 27378-2024 artfynd.xlsx
@@ -2251,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119750227</v>
+        <v>119749574</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,49 +2263,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27378, Långgöl, Sm</t>
+          <t>A 27380, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588526</v>
+        <v>588618</v>
       </c>
       <c r="R16" t="n">
-        <v>6435798</v>
+        <v>6435661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119749574</v>
+        <v>119750194</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>96888</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,31 +2374,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2409,17 +2410,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27380, Långgöl, Sm</t>
+          <t>A 27378, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588618</v>
+        <v>588531</v>
       </c>
       <c r="R17" t="n">
-        <v>6435661</v>
+        <v>6435803</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2479,7 +2480,7 @@
         <v>119750021</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,7 +2594,7 @@
         <v>119749642</v>
       </c>
       <c r="B19" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119750060</v>
+        <v>119750227</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,35 +2722,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588510</v>
+        <v>588526</v>
       </c>
       <c r="R20" t="n">
-        <v>6435794</v>
+        <v>6435798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,10 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119750194</v>
+        <v>119750060</v>
       </c>
       <c r="B21" t="n">
-        <v>96865</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,35 +2840,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588531</v>
+        <v>588510</v>
       </c>
       <c r="R21" t="n">
-        <v>6435803</v>
+        <v>6435794</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
